--- a/tools/spatial_prob_manipulations_details.xlsx
+++ b/tools/spatial_prob_manipulations_details.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20395"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LULCC_CH\Tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\CH_ValPar.CH\03_workspaces\07_Modeling\LULCC_CH\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93BDD25-2C49-40B3-9F3D-5B316D8A3AB5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A30DE0-4E83-4AC7-9EFC-09A35DD4D870}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{651BAE16-29FB-4958-8697-D574B39FF50C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{651BAE16-29FB-4958-8697-D574B39FF50C}"/>
   </bookViews>
   <sheets>
     <sheet name="Spatial_prob_perturb_suggestion" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spatial_prob_perturb_suggestion!$A$1:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Spatial_prob_perturb_suggestion!$A$1:$I$22</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,13 +30,17 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={D8018EB7-F89F-E54C-B0CE-75895A5D894E}</author>
+    <author>tc={D8018EB7-F89F-E54D-B0CE-75895A5D894E}</author>
     <author>tc={D8018EB7-F89F-E54B-B0CE-75895A5D894E}</author>
+    <author>tc={D8018EB7-F89F-E54F-B0CE-75895A5D894E}</author>
+    <author>tc={D8018EB7-F89F-E550-B0CE-75895A5D894E}</author>
     <author>tc={DC6CB4E6-37EC-FC48-9A5E-04ECF2D274DF}</author>
-    <author>tc={C39B6C8D-7179-DF44-AEE7-C18E6E52711B}</author>
-    <author>tc={D6463A77-C9E9-274B-B94A-8F4BA0933462}</author>
+    <author>tc={DC6CB4E6-37EC-FC49-9A5E-04ECF2D274DF}</author>
+    <author>tc={DC6CB4E6-37EC-FC4A-9A5E-04ECF2D274DF}</author>
   </authors>
   <commentList>
-    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{6F01B808-00D3-49DE-92E6-02799E50627C}">
+    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{6F01B808-00D3-49DE-92E6-02799E50627C}">
       <text>
         <r>
           <rPr>
@@ -47,16 +50,16 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     What is again the logic of a rural exodus in the BAU scenario?
-Antwort:
+Reply:
     Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{402ED776-0F76-4DD4-AABA-DA4B3D344E82}">
+    <comment ref="I14" authorId="1" shapeId="0" xr:uid="{402ED776-0F76-4DD4-AABA-DA4B3D344E82}">
       <text>
         <r>
           <rPr>
@@ -66,16 +69,16 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     What is again the logic of a rural exodus in the BAU scenario?
-Antwort:
+Reply:
     Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0" xr:uid="{D8018EB7-F89F-E54B-B0CE-75895A5D894E}">
+    <comment ref="I15" authorId="2" shapeId="0" xr:uid="{D8018EB7-F89F-E54B-B0CE-75895A5D894E}">
       <text>
         <r>
           <rPr>
@@ -85,16 +88,16 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     What is again the logic of a rural exodus in the BAU scenario?
-Antwort:
+Reply:
     Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
         </r>
       </text>
     </comment>
-    <comment ref="H16" authorId="0" shapeId="0" xr:uid="{1CAFC7E6-0821-499C-A0AC-A52FC69619A4}">
+    <comment ref="I17" authorId="3" shapeId="0" xr:uid="{49FAC4C3-F42B-4A16-B5FA-FB831116C489}">
       <text>
         <r>
           <rPr>
@@ -104,16 +107,16 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     What is again the logic of a rural exodus in the BAU scenario?
-Antwort:
+Reply:
     Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{49FAC4C3-F42B-4A16-B5FA-FB831116C489}">
+    <comment ref="I18" authorId="4" shapeId="0" xr:uid="{645B1E99-411A-4ECC-B3F9-0789F2C90FE5}">
       <text>
         <r>
           <rPr>
@@ -123,16 +126,16 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     What is again the logic of a rural exodus in the BAU scenario?
-Antwort:
+Reply:
     Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
         </r>
       </text>
     </comment>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{645B1E99-411A-4ECC-B3F9-0789F2C90FE5}">
+    <comment ref="H19" authorId="5" shapeId="0" xr:uid="{DC6CB4E6-37EC-FC48-9A5E-04ECF2D274DF}">
       <text>
         <r>
           <rPr>
@@ -142,16 +145,14 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    What is again the logic of a rural exodus in the BAU scenario?
-Antwort:
-    Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Here I think it’s a question of time when this land starts to shift to another class which likely is shrubland or forest. Depending on how long these processes take. </t>
         </r>
       </text>
     </comment>
-    <comment ref="G19" authorId="1" shapeId="0" xr:uid="{DC6CB4E6-37EC-FC48-9A5E-04ECF2D274DF}">
+    <comment ref="H20" authorId="6" shapeId="0" xr:uid="{309C492E-E860-43C2-B03F-4829E925F5CC}">
       <text>
         <r>
           <rPr>
@@ -161,14 +162,14 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Here I think it’s a question of time when this land starts to shift to another class which likely is shrubland or forest. Depending on how long these processes take. </t>
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="2" shapeId="0" xr:uid="{C39B6C8D-7179-DF44-AEE7-C18E6E52711B}">
+    <comment ref="H21" authorId="7" shapeId="0" xr:uid="{2BC2C279-6A71-4933-9130-A7B8727E337D}">
       <text>
         <r>
           <rPr>
@@ -178,31 +179,10 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
+          <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Here I think it’s a question of time when this land starts to shift to another class which likely is shrubland or forest. Depending on how long these processes take. </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H21" authorId="3" shapeId="0" xr:uid="{D6463A77-C9E9-274B-B94A-8F4BA0933462}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    I agree that it should have something to do with the access via the roads. 
-Antwort:
-    It could mean that all cells that have a certain distance from roads which are agriculture are more likely to transition into shrubland, open forest. I see this as agricultural aera that is not accessable where nature basically takes overt the previously managed areas. 
-Antwort:
-    I think it’s well worth to also think about the cultural element of the landscape. For example that these alpine pastures are seen as something nice and linked to swiss culture. </t>
         </r>
       </text>
     </comment>
@@ -211,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="81">
   <si>
     <t>Scenario</t>
   </si>
@@ -219,9 +199,6 @@
     <t>Driver</t>
   </si>
   <si>
-    <t>Scenario_statement</t>
-  </si>
-  <si>
     <t>LULC_class_target</t>
   </si>
   <si>
@@ -231,18 +208,12 @@
     <t>land management</t>
   </si>
   <si>
-    <t>Land management is spatially zoned: areas for agriculture, residence, recreation, biodiversity promotion are spatially strongly separated.</t>
-  </si>
-  <si>
     <t>Urban</t>
   </si>
   <si>
     <t>EI_NAT</t>
   </si>
   <si>
-    <t>strong limitation of settlement growth and land fragmentation</t>
-  </si>
-  <si>
     <t>GR_EX</t>
   </si>
   <si>
@@ -264,45 +235,15 @@
     <t>settlement development</t>
   </si>
   <si>
-    <t>Abandonment of settlements in remote rural areas</t>
-  </si>
-  <si>
-    <t>Development of small towns in mountain areas with spatial restrictions for settlement development.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Increase in buildings outside the construction zone;Industrial areas develop in an uncoordinated manner. </t>
-  </si>
-  <si>
     <t>Minor increase in probability of cells to urban outside the building zones</t>
   </si>
   <si>
-    <t>No further urban sprawl</t>
-  </si>
-  <si>
-    <t>No further urban sprawl.</t>
-  </si>
-  <si>
-    <t>Revival of settlements in remote rural areas</t>
-  </si>
-  <si>
     <t>Sites of agricultural production</t>
   </si>
   <si>
-    <t>Abandonment of poorly accessible marginal land</t>
-  </si>
-  <si>
     <t xml:space="preserve">EI_NAT </t>
   </si>
   <si>
-    <t xml:space="preserve">Abandonment of poorly accessible marginal land </t>
-  </si>
-  <si>
-    <t>Extensive cultivation of poorly accessible marginal land</t>
-  </si>
-  <si>
-    <t>decrease in probability of poorly accesible cells transitioning from Alp_past to other classes</t>
-  </si>
-  <si>
     <t>Intervention_ID</t>
   </si>
   <si>
@@ -318,114 +259,183 @@
     <t>Urban; Static</t>
   </si>
   <si>
-    <t>PAs are expanded and newly established (15% of Swiss land area protected by 2030, 17% by 2060);Site selection for new PAs prioritized 
+    <t>Check with Sven-Erik</t>
+  </si>
+  <si>
+    <t>Protection</t>
+  </si>
+  <si>
+    <t>Urban_densification</t>
+  </si>
+  <si>
+    <t>Urban_sprawl</t>
+  </si>
+  <si>
+    <t>Implemented</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Urban_migration</t>
+  </si>
+  <si>
+    <t>Rural_migration</t>
+  </si>
+  <si>
+    <t>Agri_abandonment</t>
+  </si>
+  <si>
+    <t>Agri_maintenance</t>
+  </si>
+  <si>
+    <t>Intervention_file_path</t>
+  </si>
+  <si>
+    <t>Data/Spat_prob_perturb_layers/Bulding_zones/BZ_raster.grd</t>
+  </si>
+  <si>
+    <t>Mountain_development</t>
+  </si>
+  <si>
+    <t>Use Typology of municipalities with 25 categories to identify cells and increase probability to urban</t>
+  </si>
+  <si>
+    <t>Use Typology of municipalities with 25 categories to identify cells and decrease probability to urban</t>
+  </si>
+  <si>
+    <t>Data/Spat_prob_perturb_layers/Municipality_typology/Muni_type_raster.grd</t>
+  </si>
+  <si>
+    <t>If the % difference between the means of the 90th percentile data points outside vs. inside the building zones is positive then increase the probabilities to urban of the data points outside the building zones by the % difference value otherwise if it is negative then decrease the probabilities to urban of the data points inside the building zones by the % difference value.</t>
+  </si>
+  <si>
+    <t>Increase probability to urban of cells inside building zone to 100%</t>
+  </si>
+  <si>
+    <t>Spatial_data_values</t>
+  </si>
+  <si>
+    <t>325, 326, 327, 335,338</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the % difference between the means of the 90th percentile data points outside vs. the 80th percentile data points inside the remote rural municipalities is positive then increase the probability of instances above the 90th percentile for the outside pixels by the % difference value. Else if the % difference is negative then decrease the probability of the instances above the 90th percentile inside the remote rural municipalities by the % difference value. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the % difference between the means of the 90th percentile data points outside vs. inside the mountainous municipalities is positive then increase the probability of instances above the 90th percentile for the pixels inside the mountainous municipalities by the % difference value. Else if the % difference is negative then decrease the probability of the instances above the 90th percentile outside the  municipalities by the % difference value. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the % difference between the means of the 90th percentile data points outside vs. inside the remote rural municipalities is positive then increase the probability of instances above the 90th percentile for the pixels inside the remote rural municipalities by the % difference value. Else if the % difference is negative then decrease the probability of the instances above the 90th percentile outside the  municipalities by the % difference value. </t>
+  </si>
+  <si>
+    <t>Mechanism_overview</t>
+  </si>
+  <si>
+    <t>Mechanism_detailed</t>
+  </si>
+  <si>
+    <t>Alter values of allocation parameters : Increase % of transitions with expander (incurring decrease in patcher %)</t>
+  </si>
+  <si>
+    <t>spatial_zoning</t>
+  </si>
+  <si>
+    <t>Increase in probability of transition of marginal agricultural land to non-agricultural classes</t>
+  </si>
+  <si>
+    <t>decrease in probability of marginal agricultural land transitioning to other classes</t>
+  </si>
+  <si>
+    <t>Alp_Past</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alp_Past</t>
+  </si>
+  <si>
+    <t>Identify marginal agricultural land using an index (0-1) of slope, distance to roads, inverse distance to building zones and elevation (Müller 2022). Select 90th percentile of most marginal pixels and then select 95th percentile of pixels according to probability and decrease  probability to transition from Agriculture by 5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identify marginal agricultural land using an index (0-1) of slope, distance to roads, inverse distance to building zones and elevation (Müller 2022). Select upper quartile of most marginal pixels and then select 90th percentile of pixels according to probability and  increase probability to transition from Agriculture to non-agricultural classes. Simultaneously select pixels below upper quartile of marginality and then select 90th percentile of pixels according to probability and  decrease probability to transition from Agriculture to non-agricultural classes. </t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Reduction of probability of transition to Urban, Int_AG or Perm_crops to 0 inside PAs</t>
+  </si>
+  <si>
+    <t>Data/Spat_prob_perturb_layers/Protected_areas/Future_PAs/EI_NAT_PAs_X.tif</t>
+  </si>
+  <si>
+    <t>Data/Spat_prob_perturb_layers/Protected_areas/Future_PAs/EI_SOC_PAs_X.tif</t>
+  </si>
+  <si>
+    <t>Data/Spat_prob_perturb_layers/Protected_areas/Future_PAs/EI_CUL_PAs_X.tif</t>
+  </si>
+  <si>
+    <t>If the % difference between the means of the 90th percentile data points inside vs. outside the protected areas is negative then decrease the probabilities to the target classes of the data points inside the protected by the % difference value otherwise if it is positive then increase the probabilities to the target classes of the data points outside the protected areas by the % difference value.</t>
+  </si>
+  <si>
+    <t>Spatial_zoning</t>
+  </si>
+  <si>
+    <t>Scenario_statement[@mayer2023]</t>
+  </si>
+  <si>
+    <t>Urban, Int_AG, Perm_crops</t>
+  </si>
+  <si>
+    <t>"Land management is spatially zoned: areas for agriculture, residence, recreation, biodiversity promotion are spatially strongly separated."</t>
+  </si>
+  <si>
+    <t>"strong limitation of settlement growth and land fragmentation"</t>
+  </si>
+  <si>
+    <t>"PAs are diminished (15% of Swiss land area protected by 2030, 10% by 2060); Remaining sites on agricultural unproductive land. Management under  IUCN category II"</t>
+  </si>
+  <si>
+    <t>"PAs are expanded and newly established (15% of Swiss land area protected by 2030, 17% by 2060);Site selection for new PAs prioritized 
 on agricultural unproductive land, 
-or to protect habitats of endangered species; site-specific management under  IUCN categories II or IV</t>
-  </si>
-  <si>
-    <t>PAs are expanded and newly established (17% of Swiss land area protected by 2030, 22% by 2060); Site selection for new PAs prioritizing ecosystems important for NCP provision; site-specific management under  IUCN categories II or IV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAs are expanded and newly established (17% of Swiss land area protected by 2030, 25% by 2060);Site selection for new PAs prioritizing species and landscape elements important for local communities and cultural heritage; Site-specific management under IUCN categories V or VI </t>
-  </si>
-  <si>
-    <t>PAs are expanded and newly established (20% of Swiss land area protected by 2030, 30% by 2060); Site selection for new PAs prioritizing species and habitats important for biodiversity, ecosystem processes and functions; site-specific management under IUCN category Ia or IV</t>
-  </si>
-  <si>
-    <t>Check with Sven-Erik</t>
-  </si>
-  <si>
-    <t>Protection</t>
-  </si>
-  <si>
-    <t>Urban_densification</t>
-  </si>
-  <si>
-    <t>Urban_sprawl</t>
-  </si>
-  <si>
-    <t>Implemented</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Urban_migration</t>
-  </si>
-  <si>
-    <t>Rural_migration</t>
-  </si>
-  <si>
-    <t>Agri_abandonment</t>
-  </si>
-  <si>
-    <t>Agri_maintenance</t>
-  </si>
-  <si>
-    <t>PAs are diminished (15% of Swiss land area protected by 2030, 10% by 2060); Remaining sites on agricultural unproductive land. Management under  IUCN category II -</t>
-  </si>
-  <si>
-    <t>Intervention_file_path</t>
-  </si>
-  <si>
-    <t>Data/Spat_prob_perturb_layers/Bulding_zones/BZ_raster.grd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abandonment of settlements in remote rural areas </t>
-  </si>
-  <si>
-    <t>Mountain_development</t>
-  </si>
-  <si>
-    <t>Use Typology of municipalities with 25 categories to identify cells and increase probability to urban</t>
-  </si>
-  <si>
-    <t>Use Typology of municipalities with 25 categories to identify cells and decrease probability to urban</t>
-  </si>
-  <si>
-    <t>Data/Spat_prob_perturb_layers/Municipality_typology/Muni_type_raster.grd</t>
-  </si>
-  <si>
-    <t>If the % difference between the means of the 90th percentile data points outside vs. inside the building zones is positive then increase the probabilities to urban of the data points outside the building zones by the % difference value otherwise if it is negative then decrease the probabilities to urban of the data points inside the building zones by the % difference value.</t>
-  </si>
-  <si>
-    <t>Increase probability to urban of cells inside building zone to 100%</t>
-  </si>
-  <si>
-    <t>Spatial_data_values</t>
-  </si>
-  <si>
-    <t>325, 326, 327, 335,338</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the % difference between the means of the 90th percentile data points outside vs. the 80th percentile data points inside the remote rural municipalities is positive then increase the probability of instances above the 90th percentile for the outside pixels by the % difference value. Else if the % difference is negative then decrease the probability of the instances above the 90th percentile inside the remote rural municipalities by the % difference value. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the % difference between the means of the 90th percentile data points outside vs. inside the mountainous municipalities is positive then increase the probability of instances above the 90th percentile for the pixels inside the mountainous municipalities by the % difference value. Else if the % difference is negative then decrease the probability of the instances above the 90th percentile outside the  municipalities by the % difference value. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the % difference between the means of the 90th percentile data points outside vs. inside the remote rural municipalities is positive then increase the probability of instances above the 90th percentile for the pixels inside the remote rural municipalities by the % difference value. Else if the % difference is negative then decrease the probability of the instances above the 90th percentile outside the  municipalities by the % difference value. </t>
-  </si>
-  <si>
-    <t>Int_AG, Alp_Past</t>
-  </si>
-  <si>
-    <t>Mechanism_overview</t>
-  </si>
-  <si>
-    <t>Mechanism_detailed</t>
-  </si>
-  <si>
-    <t>Alter values of allocation parameters : Increase % of transitions with expander (incurring decrease in patcher %)</t>
-  </si>
-  <si>
-    <t>Identify marginal agricultural land using an index (0-1) of slope, distance to roads and elevation (Müller 2022). Select 90th percentile of most marginal pixels increase probability to transition from Agriculture</t>
-  </si>
-  <si>
-    <t>spatial_zoning</t>
+or to protect habitats of endangered species; site-specific management under  IUCN categories II or IV"</t>
+  </si>
+  <si>
+    <t>"PAs are expanded and newly established (17% of Swiss land area protected by 2030, 22% by 2060); Site selection for new PAs prioritizing ecosystems important for NCP provision; site-specific management under  IUCN categories II or IV"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"PAs are expanded and newly established (17% of Swiss land area protected by 2030, 25% by 2060);Site selection for new PAs prioritizing species and landscape elements important for local communities and cultural heritage; Site-specific management under IUCN categories V or VI" </t>
+  </si>
+  <si>
+    <t>"PAs are expanded and newly established (20% of Swiss land area protected by 2030, 30% by 2060); Site selection for new PAs prioritizing species and habitats important for biodiversity, ecosystem processes and functions; site-specific management under IUCN category Ia or IV"</t>
+  </si>
+  <si>
+    <t>"No further urban sprawl"</t>
+  </si>
+  <si>
+    <t>"No further urban sprawl."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Increase in buildings outside the construction zone;Industrial areas develop in an uncoordinated manner." </t>
+  </si>
+  <si>
+    <t>"Development of small towns in mountain areas with spatial restrictions for settlement development."</t>
+  </si>
+  <si>
+    <t>"Abandonment of settlements in remote rural areas."</t>
+  </si>
+  <si>
+    <t>"Revival of settlements in remote rural areas"</t>
+  </si>
+  <si>
+    <t>"Abandonment of poorly accessible marginal land"</t>
+  </si>
+  <si>
+    <t>"Extensive cultivation of poorly accessible marginal land"</t>
+  </si>
+  <si>
+    <t>Spatial prioritization map produced with the conservation prioritization software Zonation [@lehtomäki2013] using modelled spatial data for 7 NCPs: nutrient retention; recreation; landscape suitability for pollination; pest control; hazard regulation; carbon storage in vegetation; air quality regulation.</t>
   </si>
 </sst>
 </file>
@@ -524,7 +534,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -547,11 +557,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -646,6 +669,10 @@
     <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -966,96 +993,67 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="I2" dT="2023-01-24T08:06:04.18" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{BAA875D6-3207-45F1-AFB0-27EB2561448A}">
-    <text>Will be be doing this for all scenarios but in a systematic stepwise way? For example then for the GE Scenario we would increase the probability?</text>
-  </threadedComment>
-  <threadedComment ref="I3" dT="2023-01-26T10:33:48.12" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{71D96C11-9C84-504E-8ADA-B33D9CF9EEAB}">
-    <text xml:space="preserve">I find this to be a good indicator for the % increase. If we look at when urban growth was uncoordinated and what the historic rates are. </text>
-  </threadedComment>
-  <threadedComment ref="I3" dT="2023-01-26T10:34:34.87" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{E2EACF15-7856-6040-8D3B-E06C5BB18BED}" parentId="{71D96C11-9C84-504E-8ADA-B33D9CF9EEAB}">
-    <text>The question I have here is if we also steer this with the transition rates or not?</text>
-  </threadedComment>
-  <threadedComment ref="H4" dT="2023-01-26T10:37:29.32" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{B2F70728-6A72-1144-9788-E5C3B1B3F177}">
-    <text xml:space="preserve">I agree that if we have the transition rates following the development as we decided it makes sense to see how the dynamics develope. </text>
-  </threadedComment>
-  <threadedComment ref="H5" dT="2023-01-27T07:28:54.77" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{CCB0772F-ED47-884E-AAE7-D3BCD408F593}">
-    <text xml:space="preserve">Do we assume/allow that the building zones will all be used in each one of the scenarios? Or is there a scenario where some building zones area decreased again. </text>
-  </threadedComment>
-  <threadedComment ref="H5" dT="2023-01-27T08:14:36.66" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{FD636061-6229-F148-8B7A-BB73CCCCD968}" parentId="{CCB0772F-ED47-884E-AAE7-D3BCD408F593}">
-    <text>If I look at the overlap between the Land Use (2018) and the building zones then the building zones seem to be very little area. If we see the option for a scenario that the there will be an increase in building zones (scenarios with lots of population) then we could also use a buffer of some 100 meters around the building zones.</text>
-  </threadedComment>
-  <threadedComment ref="H6" dT="2023-01-24T08:47:00.77" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{84D8B7E6-33EB-AD47-B285-C536C0FD2B69}">
-    <text>How do these two interventions complement or cancel each other out? Does an increase within the building zone have an effect on the cells outside the building zone?</text>
-  </threadedComment>
-  <threadedComment ref="I6" dT="2023-01-24T08:54:16.61" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{8C9AEFD0-FF1C-3447-B72E-A587AE7020B6}">
-    <text xml:space="preserve">We could say that we reduce to probability to become cells in all areas that do not attach to a larger consortium of urban cells (like 2 or 3). </text>
-  </threadedComment>
-  <threadedComment ref="I15" dT="2023-01-24T08:04:28.61" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{3B69D198-9CEF-4D52-8F56-260C72A8D7E7}">
-    <text>We cold potentially use the municipality polygons in a certain hight and alter the probability of urban cells there?</text>
-  </threadedComment>
-  <threadedComment ref="G17" dT="2023-01-27T08:18:37.62" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{6F948D1D-9913-4D4B-8D3C-CD90C016E602}">
+  <threadedComment ref="I13" dT="2023-01-27T08:18:37.62" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{D8018EB7-F89F-E54C-B0CE-75895A5D894E}">
     <text>What is again the logic of a rural exodus in the BAU scenario?</text>
   </threadedComment>
-  <threadedComment ref="G17" dT="2023-01-27T08:20:17.15" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{B448348D-5B71-1F46-8184-5B4AD596E784}" parentId="{6F948D1D-9913-4D4B-8D3C-CD90C016E602}">
+  <threadedComment ref="I13" dT="2023-01-27T08:20:17.15" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{EFF6F1CE-C45F-1B43-99DD-C9DDF4B66D7B}" parentId="{D8018EB7-F89F-E54C-B0CE-75895A5D894E}">
     <text xml:space="preserve">Because in the BAU I also see the devlopment with all the holiday houses to continue.  </text>
   </threadedComment>
-  <threadedComment ref="H17" dT="2023-01-27T08:18:37.62" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{D8018EB7-F89F-E54B-B0CE-75895A5D894E}">
+  <threadedComment ref="I14" dT="2023-01-27T08:18:37.62" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{D8018EB7-F89F-E54D-B0CE-75895A5D894E}">
     <text>What is again the logic of a rural exodus in the BAU scenario?</text>
   </threadedComment>
-  <threadedComment ref="H17" dT="2023-01-27T08:20:17.15" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{EFF6F1CE-C45F-1B42-99DD-C9DDF4B66D7B}" parentId="{D8018EB7-F89F-E54B-B0CE-75895A5D894E}">
+  <threadedComment ref="I14" dT="2023-01-27T08:20:17.15" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{EFF6F1CE-C45F-1B44-99DD-C9DDF4B66D7B}" parentId="{D8018EB7-F89F-E54D-B0CE-75895A5D894E}">
     <text xml:space="preserve">Because in the BAU I also see the devlopment with all the holiday houses to continue.  </text>
   </threadedComment>
-  <threadedComment ref="I18" dT="2023-01-24T08:19:26.89" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{B98E91AB-936F-4B33-84EA-BF63F06E08C8}">
-    <text xml:space="preserve">This is a good question and I would argue again really dependent on the scenarios themself. I interpret the abandonment of settlements in remote rural areas more in a way that places such as ski resorts, agriculture in the alps and so on will be reduced. Settlements such as mountain/alpine villages will certainly not become abandoned in any case. But what I can imagine will happen is for example if you have some infrastructure or agriculture building in the higher mountains that they will be reduced. </text>
+  <threadedComment ref="I15" dT="2023-01-27T08:18:37.62" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{D8018EB7-F89F-E54B-B0CE-75895A5D894E}">
+    <text>What is again the logic of a rural exodus in the BAU scenario?</text>
   </threadedComment>
-  <threadedComment ref="I18" dT="2023-01-24T08:33:53.73" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{80BE4C7E-9789-DB47-B1B4-FC6D5BFD31B2}" parentId="{B98E91AB-936F-4B33-84EA-BF63F06E08C8}">
-    <text>The problem here I see is that there are only little cells in these rural areas.</text>
+  <threadedComment ref="I15" dT="2023-01-27T08:20:17.15" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{EFF6F1CE-C45F-1B42-99DD-C9DDF4B66D7B}" parentId="{D8018EB7-F89F-E54B-B0CE-75895A5D894E}">
+    <text xml:space="preserve">Because in the BAU I also see the devlopment with all the holiday houses to continue.  </text>
   </threadedComment>
-  <threadedComment ref="I20" dT="2023-01-24T10:02:21.65" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{194B286F-08F7-E14C-9C14-27B4DC019FBE}">
-    <text>This is not entirely clear to me as urban can only become static?</text>
+  <threadedComment ref="I17" dT="2023-01-27T08:18:37.62" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{D8018EB7-F89F-E54F-B0CE-75895A5D894E}">
+    <text>What is again the logic of a rural exodus in the BAU scenario?</text>
   </threadedComment>
-  <threadedComment ref="I20" dT="2023-01-27T08:17:39.15" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{3F72F080-A1A6-814B-8099-525714674248}" parentId="{194B286F-08F7-E14C-9C14-27B4DC019FBE}">
-    <text>One thing I can imagine is that we also create a transition of urban to other classes associated with green infrastructure. For example when urban areas are converted to parks or nature areas.</text>
+  <threadedComment ref="I17" dT="2023-01-27T08:20:17.15" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{EFF6F1CE-C45F-1B46-99DD-C9DDF4B66D7B}" parentId="{D8018EB7-F89F-E54F-B0CE-75895A5D894E}">
+    <text xml:space="preserve">Because in the BAU I also see the devlopment with all the holiday houses to continue.  </text>
   </threadedComment>
-  <threadedComment ref="G21" dT="2023-01-27T08:23:49.76" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{DC6CB4E6-37EC-FC48-9A5E-04ECF2D274DF}">
+  <threadedComment ref="I18" dT="2023-01-27T08:18:37.62" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{D8018EB7-F89F-E550-B0CE-75895A5D894E}">
+    <text>What is again the logic of a rural exodus in the BAU scenario?</text>
+  </threadedComment>
+  <threadedComment ref="I18" dT="2023-01-27T08:20:17.15" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{EFF6F1CE-C45F-1B47-99DD-C9DDF4B66D7B}" parentId="{D8018EB7-F89F-E550-B0CE-75895A5D894E}">
+    <text xml:space="preserve">Because in the BAU I also see the devlopment with all the holiday houses to continue.  </text>
+  </threadedComment>
+  <threadedComment ref="H19" dT="2023-01-27T08:23:49.76" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{DC6CB4E6-37EC-FC48-9A5E-04ECF2D274DF}">
     <text xml:space="preserve">Here I think it’s a question of time when this land starts to shift to another class which likely is shrubland or forest. Depending on how long these processes take. </text>
   </threadedComment>
-  <threadedComment ref="H21" dT="2023-01-27T08:23:49.76" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{C39B6C8D-7179-DF44-AEE7-C18E6E52711B}">
+  <threadedComment ref="H20" dT="2023-01-27T08:23:49.76" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{DC6CB4E6-37EC-FC49-9A5E-04ECF2D274DF}">
     <text xml:space="preserve">Here I think it’s a question of time when this land starts to shift to another class which likely is shrubland or forest. Depending on how long these processes take. </text>
   </threadedComment>
-  <threadedComment ref="I22" dT="2023-01-24T10:34:55.85" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{26374558-14BA-D648-8DE7-557EADE9FD07}">
-    <text>Why is this part of the BAU?</text>
-  </threadedComment>
-  <threadedComment ref="I23" dT="2023-01-24T10:34:40.76" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{D6463A77-C9E9-274B-B94A-8F4BA0933462}">
-    <text xml:space="preserve">I agree that it should have something to do with the access via the roads. </text>
-  </threadedComment>
-  <threadedComment ref="I23" dT="2023-01-24T10:36:53.69" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{CF11FBA9-4D01-B04F-BDCC-C47FA7554EC1}" parentId="{D6463A77-C9E9-274B-B94A-8F4BA0933462}">
-    <text xml:space="preserve">It could mean that all cells that have a certain distance from roads which are agriculture are more likely to transition into shrubland, open forest. I see this as agricultural aera that is not accessable where nature basically takes overt the previously managed areas. </text>
-  </threadedComment>
-  <threadedComment ref="I23" dT="2023-01-24T10:37:51.69" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{6744A664-D6F5-5F4D-942E-A4649811579B}" parentId="{D6463A77-C9E9-274B-B94A-8F4BA0933462}">
-    <text xml:space="preserve">I think it’s well worth to also think about the cultural element of the landscape. For example that these alpine pastures are seen as something nice and linked to swiss culture. </text>
+  <threadedComment ref="H21" dT="2023-01-27T08:23:49.76" personId="{56CA59CE-2B6D-4E09-AFFC-FE8B4E306026}" id="{DC6CB4E6-37EC-FC4A-9A5E-04ECF2D274DF}">
+    <text xml:space="preserve">Here I think it’s a question of time when this land starts to shift to another class which likely is shrubland or forest. Depending on how long these processes take. </text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ACA9C24-578D-43A9-82B8-6427B2AE2C72}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.42578125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="43" style="1" customWidth="1"/>
-    <col min="9" max="9" width="73.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="3" max="4" width="52.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="43" style="1" customWidth="1"/>
+    <col min="9" max="9" width="59.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="73.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1063,667 +1061,750 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="68.849999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="K6" s="25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="B11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15">
+        <v>314</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="31">
+        <v>314334</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="H19" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="23" t="s">
+      <c r="I19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="23" t="s">
+      <c r="B20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="25"/>
-    </row>
-    <row r="5" spans="1:10" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="25"/>
-    </row>
-    <row r="6" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="25"/>
-    </row>
-    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="B22" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="25"/>
-    </row>
-    <row r="8" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="25"/>
-    </row>
-    <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="5" t="s">
+      <c r="C22" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="E22" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="H22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="135" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="150" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="15">
-        <v>314</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="15" t="s">
+      <c r="I22" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="J13" s="19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="150" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="31">
-        <v>314334</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="165" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="J15" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="165" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="165" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="J17" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="150" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="J18" s="27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="21"/>
-    </row>
-    <row r="20" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="21"/>
-    </row>
-    <row r="21" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="J22" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="21"/>
-    </row>
-    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="22"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C23" s="16"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D23" s="16"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C24" s="16"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D24" s="16"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
     </row>
   </sheetData>
-  <sortState ref="A2:J25">
+  <sortState ref="A2:K25">
     <sortCondition ref="B1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1733,20 +1814,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1f0a4303-6c30-4be1-95b2-d3f846a6dc61" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1f0a4303-6c30-4be1-95b2-d3f846a6dc61" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1973,26 +2054,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75168B6-E7FC-4BE5-9F9D-42A41711F424}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9B5ECA8-FED0-4F9E-AF48-225E059A944A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1f0a4303-6c30-4be1-95b2-d3f846a6dc61"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="35f94e42-e4d5-4a2a-b205-129e91914919"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9B5ECA8-FED0-4F9E-AF48-225E059A944A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75168B6-E7FC-4BE5-9F9D-42A41711F424}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="35f94e42-e4d5-4a2a-b205-129e91914919"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="1f0a4303-6c30-4be1-95b2-d3f846a6dc61"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/tools/spatial_prob_manipulations_details.xlsx
+++ b/tools/spatial_prob_manipulations_details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\CH_ValPar.CH\03_workspaces\07_Modeling\LULCC_CH\Tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bblack\switchdrive\C.3_Modelling\LULCC_CH\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A30DE0-4E83-4AC7-9EFC-09A35DD4D870}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8F5CA5-13DD-4047-9E29-0A617B0A58EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{651BAE16-29FB-4958-8697-D574B39FF50C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{651BAE16-29FB-4958-8697-D574B39FF50C}"/>
   </bookViews>
   <sheets>
     <sheet name="Spatial_prob_perturb_suggestion" sheetId="1" r:id="rId1"/>
@@ -42,148 +42,76 @@
   <commentList>
     <comment ref="I13" authorId="0" shapeId="0" xr:uid="{6F01B808-00D3-49DE-92E6-02799E50627C}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     What is again the logic of a rural exodus in the BAU scenario?
 Reply:
     Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
-        </r>
       </text>
     </comment>
     <comment ref="I14" authorId="1" shapeId="0" xr:uid="{402ED776-0F76-4DD4-AABA-DA4B3D344E82}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     What is again the logic of a rural exodus in the BAU scenario?
 Reply:
     Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
-        </r>
       </text>
     </comment>
     <comment ref="I15" authorId="2" shapeId="0" xr:uid="{D8018EB7-F89F-E54B-B0CE-75895A5D894E}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     What is again the logic of a rural exodus in the BAU scenario?
 Reply:
     Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
-        </r>
       </text>
     </comment>
     <comment ref="I17" authorId="3" shapeId="0" xr:uid="{49FAC4C3-F42B-4A16-B5FA-FB831116C489}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     What is again the logic of a rural exodus in the BAU scenario?
 Reply:
     Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
-        </r>
       </text>
     </comment>
     <comment ref="I18" authorId="4" shapeId="0" xr:uid="{645B1E99-411A-4ECC-B3F9-0789F2C90FE5}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     What is again the logic of a rural exodus in the BAU scenario?
 Reply:
     Because in the BAU I also see the devlopment with all the holiday houses to continue.  </t>
-        </r>
       </text>
     </comment>
     <comment ref="H19" authorId="5" shapeId="0" xr:uid="{DC6CB4E6-37EC-FC48-9A5E-04ECF2D274DF}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Here I think it’s a question of time when this land starts to shift to another class which likely is shrubland or forest. Depending on how long these processes take. </t>
-        </r>
       </text>
     </comment>
     <comment ref="H20" authorId="6" shapeId="0" xr:uid="{309C492E-E860-43C2-B03F-4829E925F5CC}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Here I think it’s a question of time when this land starts to shift to another class which likely is shrubland or forest. Depending on how long these processes take. </t>
-        </r>
       </text>
     </comment>
     <comment ref="H21" authorId="7" shapeId="0" xr:uid="{2BC2C279-6A71-4933-9130-A7B8727E337D}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Here I think it’s a question of time when this land starts to shift to another class which likely is shrubland or forest. Depending on how long these processes take. </t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -191,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="86">
   <si>
     <t>Scenario</t>
   </si>
@@ -247,9 +175,6 @@
     <t>Intervention_ID</t>
   </si>
   <si>
-    <t>probability of Urban transitions increased inside building zones (using all classes in the building zones)</t>
-  </si>
-  <si>
     <t>alter values of allocation parameter (patcher vs. Expander)</t>
   </si>
   <si>
@@ -298,12 +223,6 @@
     <t>Mountain_development</t>
   </si>
   <si>
-    <t>Use Typology of municipalities with 25 categories to identify cells and increase probability to urban</t>
-  </si>
-  <si>
-    <t>Use Typology of municipalities with 25 categories to identify cells and decrease probability to urban</t>
-  </si>
-  <si>
     <t>Data/Spat_prob_perturb_layers/Municipality_typology/Muni_type_raster.grd</t>
   </si>
   <si>
@@ -337,28 +256,16 @@
     <t>Mechanism_detailed</t>
   </si>
   <si>
-    <t>Alter values of allocation parameters : Increase % of transitions with expander (incurring decrease in patcher %)</t>
-  </si>
-  <si>
     <t>spatial_zoning</t>
   </si>
   <si>
     <t>Increase in probability of transition of marginal agricultural land to non-agricultural classes</t>
   </si>
   <si>
-    <t>decrease in probability of marginal agricultural land transitioning to other classes</t>
-  </si>
-  <si>
     <t>Alp_Past</t>
   </si>
   <si>
     <t xml:space="preserve"> Alp_Past</t>
-  </si>
-  <si>
-    <t>Identify marginal agricultural land using an index (0-1) of slope, distance to roads, inverse distance to building zones and elevation (Müller 2022). Select 90th percentile of most marginal pixels and then select 95th percentile of pixels according to probability and decrease  probability to transition from Agriculture by 5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identify marginal agricultural land using an index (0-1) of slope, distance to roads, inverse distance to building zones and elevation (Müller 2022). Select upper quartile of most marginal pixels and then select 90th percentile of pixels according to probability and  increase probability to transition from Agriculture to non-agricultural classes. Simultaneously select pixels below upper quartile of marginality and then select 90th percentile of pixels according to probability and  decrease probability to transition from Agriculture to non-agricultural classes. </t>
   </si>
   <si>
     <t>N</t>
@@ -435,7 +342,43 @@
     <t>"Extensive cultivation of poorly accessible marginal land"</t>
   </si>
   <si>
-    <t>Spatial prioritization map produced with the conservation prioritization software Zonation [@lehtomäki2013] using modelled spatial data for 7 NCPs: nutrient retention; recreation; landscape suitability for pollination; pest control; hazard regulation; carbon storage in vegetation; air quality regulation.</t>
+    <t>Increase % of transitions with expander (incurring decrease in patcher %)</t>
+  </si>
+  <si>
+    <t>Increase probability to urban of cells in Mountainous municipalities</t>
+  </si>
+  <si>
+    <t>Decrease probability to urban of cells in remote rural municipalities</t>
+  </si>
+  <si>
+    <t>Increase probability to urban of cells in remote rural municipalities</t>
+  </si>
+  <si>
+    <t>Decrease in probability of marginal agricultural land transitioning to other classes</t>
+  </si>
+  <si>
+    <t>Select 90th percentile of most marginal pixels and then select 95th percentile of pixels according to probability and decrease  probability to transition from Agriculture by 5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select upper quartile of most marginal pixels and then select 90th percentile of pixels according to probability and  increase probability to transition from Agriculture to non-agricultural classes. Simultaneously select pixels below upper quartile of marginality and then select 90th percentile of pixels according to probability and  decrease probability to transition from Agriculture to non-agricultural classes. </t>
+  </si>
+  <si>
+    <t>Probability of Urban transitions increased inside building zones (using all classes in the building zones)</t>
+  </si>
+  <si>
+    <t>Marginal agricultural land identified using an index (0-1) of slope, distance to roads, inverse distance to building zones and elevation[@muller_verbuschung_2022].</t>
+  </si>
+  <si>
+    <t>Areas to modify urban development identified using the Swiss building zones geodata \citepalias{ARE_2022}.</t>
+  </si>
+  <si>
+    <t>Mountainous municipalities identified using the Swiss typology of municipalities (25 categories)\citepalias{swiss_federal_office_for_statistics_sfso_typology_2023}</t>
+  </si>
+  <si>
+    <t>For details see @sec-PA_process</t>
+  </si>
+  <si>
+    <t>Remote rural municipalities identified using the Swiss typology of municipalities (25 categories)\citepalias{swiss_federal_office_for_statistics_sfso_typology_2023}</t>
   </si>
 </sst>
 </file>
@@ -1038,22 +981,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ACA9C24-578D-43A9-82B8-6427B2AE2C72}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="4" width="52.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="25.3984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.3984375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="4" width="52.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.3984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.3984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.3984375" style="1" customWidth="1"/>
     <col min="8" max="8" width="43" style="1" customWidth="1"/>
-    <col min="9" max="9" width="59.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="73.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="59.59765625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="73.73046875" style="1" customWidth="1"/>
     <col min="11" max="11" width="19" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.85546875" style="1"/>
+    <col min="12" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1061,13 +1004,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -1076,19 +1019,19 @@
         <v>17</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1096,34 +1039,34 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1131,34 +1074,34 @@
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="23" t="s">
         <v>7</v>
       </c>
@@ -1166,19 +1109,19 @@
         <v>8</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>10</v>
@@ -1187,13 +1130,13 @@
         <v>10</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="122.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="23" t="s">
         <v>11</v>
       </c>
@@ -1201,19 +1144,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>10</v>
@@ -1222,13 +1165,13 @@
         <v>10</v>
       </c>
       <c r="J5" s="25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="68.849999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="68.849999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="23" t="s">
         <v>3</v>
       </c>
@@ -1236,34 +1179,34 @@
         <v>8</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A7" s="23" t="s">
         <v>12</v>
       </c>
@@ -1271,32 +1214,34 @@
         <v>8</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="24"/>
+        <v>63</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>84</v>
+      </c>
       <c r="E7" s="23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="46.5" x14ac:dyDescent="0.45">
       <c r="A8" s="23" t="s">
         <v>6</v>
       </c>
@@ -1304,32 +1249,34 @@
         <v>8</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="24"/>
+        <v>64</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>84</v>
+      </c>
       <c r="E8" s="23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -1337,32 +1284,34 @@
         <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="E9" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
@@ -1370,32 +1319,34 @@
         <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="E10" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>3</v>
       </c>
@@ -1403,32 +1354,34 @@
         <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="E11" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A12" s="13" t="s">
         <v>7</v>
       </c>
@@ -1436,32 +1389,34 @@
         <v>13</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="14"/>
+        <v>67</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="E12" s="18" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A13" s="15" t="s">
         <v>6</v>
       </c>
@@ -1469,9 +1424,11 @@
         <v>13</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="15"/>
+        <v>68</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>83</v>
+      </c>
       <c r="E13" s="15">
         <v>314</v>
       </c>
@@ -1479,22 +1436,22 @@
         <v>5</v>
       </c>
       <c r="G13" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>37</v>
-      </c>
       <c r="K13" s="19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A14" s="15" t="s">
         <v>3</v>
       </c>
@@ -1502,9 +1459,11 @@
         <v>13</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="15"/>
+        <v>68</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>83</v>
+      </c>
       <c r="E14" s="31">
         <v>314334</v>
       </c>
@@ -1512,22 +1471,22 @@
         <v>5</v>
       </c>
       <c r="G14" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="28" t="s">
-        <v>37</v>
-      </c>
       <c r="K14" s="19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
@@ -1535,32 +1494,34 @@
         <v>13</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="8"/>
+        <v>69</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="E15" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J15" s="29" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
         <v>6</v>
       </c>
@@ -1568,32 +1529,34 @@
         <v>13</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="7"/>
+        <v>69</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="E16" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="s">
         <v>3</v>
       </c>
@@ -1601,32 +1564,34 @@
         <v>13</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="7"/>
+        <v>69</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="E17" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J17" s="29" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A18" s="26" t="s">
         <v>12</v>
       </c>
@@ -1634,32 +1599,34 @@
         <v>13</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="26"/>
+        <v>70</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>85</v>
+      </c>
       <c r="E18" s="26" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F18" s="26" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K18" s="27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A19" s="9" t="s">
         <v>3</v>
       </c>
@@ -1667,32 +1634,34 @@
         <v>15</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="10"/>
+        <v>71</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="E19" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K19" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A20" s="9" t="s">
         <v>11</v>
       </c>
@@ -1700,32 +1669,34 @@
         <v>15</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="10"/>
+        <v>71</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="E20" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A21" s="9" t="s">
         <v>16</v>
       </c>
@@ -1733,32 +1704,34 @@
         <v>15</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" s="10"/>
+        <v>71</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="E21" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A22" s="11" t="s">
         <v>12</v>
       </c>
@@ -1766,45 +1739,47 @@
         <v>15</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="12"/>
+        <v>72</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>81</v>
+      </c>
       <c r="E22" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
     </row>
   </sheetData>
-  <sortState ref="A2:K25">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K25">
     <sortCondition ref="B1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1822,15 +1797,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100EEE3694774EF754A8CC6FC6FA5E27970" ma:contentTypeVersion="13" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="d93f88a0a8255bfb930f7a727db686ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f0a4303-6c30-4be1-95b2-d3f846a6dc61" xmlns:ns4="35f94e42-e4d5-4a2a-b205-129e91914919" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd2b915ebf31ecc04d3ae81b403b739a" ns3:_="" ns4:_="">
     <xsd:import namespace="1f0a4303-6c30-4be1-95b2-d3f846a6dc61"/>
@@ -2053,6 +2019,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9B5ECA8-FED0-4F9E-AF48-225E059A944A}">
   <ds:schemaRefs>
@@ -2071,14 +2046,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75168B6-E7FC-4BE5-9F9D-42A41711F424}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF3CE86-C263-48A8-AB0F-CFFD6601505F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2095,4 +2062,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75168B6-E7FC-4BE5-9F9D-42A41711F424}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tools/spatial_prob_manipulations_details.xlsx
+++ b/tools/spatial_prob_manipulations_details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bblack\switchdrive\C.3_Modelling\LULCC_CH\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8F5CA5-13DD-4047-9E29-0A617B0A58EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C64F89B-6726-49EE-9BD3-6FC907EDC402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{651BAE16-29FB-4958-8697-D574B39FF50C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{651BAE16-29FB-4958-8697-D574B39FF50C}"/>
   </bookViews>
   <sheets>
     <sheet name="Spatial_prob_perturb_suggestion" sheetId="1" r:id="rId1"/>
@@ -178,12 +178,6 @@
     <t>alter values of allocation parameter (patcher vs. Expander)</t>
   </si>
   <si>
-    <t>Urban; Int_Ag; Open_Forest; Grassland; Perm_Crops, Alp_Past</t>
-  </si>
-  <si>
-    <t>Urban; Static</t>
-  </si>
-  <si>
     <t>Check with Sven-Erik</t>
   </si>
   <si>
@@ -379,6 +373,12 @@
   </si>
   <si>
     <t>Remote rural municipalities identified using the Swiss typology of municipalities (25 categories)\citepalias{swiss_federal_office_for_statistics_sfso_typology_2023}</t>
+  </si>
+  <si>
+    <t>Urban, Int_Ag, Open_Forest, Grassland, Perm_Crops, Alp_Past</t>
+  </si>
+  <si>
+    <t>Urban, Static</t>
   </si>
 </sst>
 </file>
@@ -981,22 +981,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ACA9C24-578D-43A9-82B8-6427B2AE2C72}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.3984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.3984375" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="4" width="52.59765625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.3984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.3984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.3984375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="4" width="52.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" style="1" customWidth="1"/>
     <col min="8" max="8" width="43" style="1" customWidth="1"/>
-    <col min="9" max="9" width="59.59765625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="73.73046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="59.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="73.7109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="19" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.86328125" style="1"/>
+    <col min="12" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1004,13 +1004,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -1019,19 +1019,19 @@
         <v>17</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1039,34 +1039,34 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1074,34 +1074,34 @@
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>7</v>
       </c>
@@ -1109,19 +1109,19 @@
         <v>8</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>10</v>
@@ -1130,13 +1130,13 @@
         <v>10</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="122.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
         <v>11</v>
       </c>
@@ -1144,19 +1144,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>10</v>
@@ -1165,13 +1165,13 @@
         <v>10</v>
       </c>
       <c r="J5" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="68.849999999999994" customHeight="1" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="68.849999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>3</v>
       </c>
@@ -1179,34 +1179,34 @@
         <v>8</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="J6" s="33" t="s">
-        <v>52</v>
-      </c>
       <c r="K6" s="25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>12</v>
       </c>
@@ -1214,34 +1214,34 @@
         <v>8</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="46.5" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
         <v>6</v>
       </c>
@@ -1249,34 +1249,34 @@
         <v>8</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H8" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -1284,34 +1284,34 @@
         <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
@@ -1319,34 +1319,34 @@
         <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>3</v>
       </c>
@@ -1354,34 +1354,34 @@
         <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>7</v>
       </c>
@@ -1389,34 +1389,34 @@
         <v>13</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>6</v>
       </c>
@@ -1424,10 +1424,10 @@
         <v>13</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E13" s="15">
         <v>314</v>
@@ -1436,22 +1436,22 @@
         <v>5</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>3</v>
       </c>
@@ -1459,10 +1459,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E14" s="31">
         <v>314334</v>
@@ -1471,22 +1471,22 @@
         <v>5</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
@@ -1494,34 +1494,34 @@
         <v>13</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J15" s="29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>6</v>
       </c>
@@ -1529,34 +1529,34 @@
         <v>13</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>3</v>
       </c>
@@ -1564,34 +1564,34 @@
         <v>13</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J17" s="29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>12</v>
       </c>
@@ -1599,34 +1599,34 @@
         <v>13</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F18" s="26" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K18" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>3</v>
       </c>
@@ -1634,34 +1634,34 @@
         <v>15</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K19" s="21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>11</v>
       </c>
@@ -1669,34 +1669,34 @@
         <v>15</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>16</v>
       </c>
@@ -1704,34 +1704,34 @@
         <v>15</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>12</v>
       </c>
@@ -1739,42 +1739,42 @@
         <v>15</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
     </row>
@@ -1797,6 +1797,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100EEE3694774EF754A8CC6FC6FA5E27970" ma:contentTypeVersion="13" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="d93f88a0a8255bfb930f7a727db686ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f0a4303-6c30-4be1-95b2-d3f846a6dc61" xmlns:ns4="35f94e42-e4d5-4a2a-b205-129e91914919" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd2b915ebf31ecc04d3ae81b403b739a" ns3:_="" ns4:_="">
     <xsd:import namespace="1f0a4303-6c30-4be1-95b2-d3f846a6dc61"/>
@@ -2019,15 +2028,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9B5ECA8-FED0-4F9E-AF48-225E059A944A}">
   <ds:schemaRefs>
@@ -2046,6 +2046,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75168B6-E7FC-4BE5-9F9D-42A41711F424}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF3CE86-C263-48A8-AB0F-CFFD6601505F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2062,12 +2070,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75168B6-E7FC-4BE5-9F9D-42A41711F424}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tools/spatial_prob_manipulations_details.xlsx
+++ b/tools/spatial_prob_manipulations_details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bblack\switchdrive\C.3_Modelling\LULCC_CH\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C64F89B-6726-49EE-9BD3-6FC907EDC402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8F5CA5-13DD-4047-9E29-0A617B0A58EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{651BAE16-29FB-4958-8697-D574B39FF50C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{651BAE16-29FB-4958-8697-D574B39FF50C}"/>
   </bookViews>
   <sheets>
     <sheet name="Spatial_prob_perturb_suggestion" sheetId="1" r:id="rId1"/>
@@ -178,6 +178,12 @@
     <t>alter values of allocation parameter (patcher vs. Expander)</t>
   </si>
   <si>
+    <t>Urban; Int_Ag; Open_Forest; Grassland; Perm_Crops, Alp_Past</t>
+  </si>
+  <si>
+    <t>Urban; Static</t>
+  </si>
+  <si>
     <t>Check with Sven-Erik</t>
   </si>
   <si>
@@ -373,12 +379,6 @@
   </si>
   <si>
     <t>Remote rural municipalities identified using the Swiss typology of municipalities (25 categories)\citepalias{swiss_federal_office_for_statistics_sfso_typology_2023}</t>
-  </si>
-  <si>
-    <t>Urban, Int_Ag, Open_Forest, Grassland, Perm_Crops, Alp_Past</t>
-  </si>
-  <si>
-    <t>Urban, Static</t>
   </si>
 </sst>
 </file>
@@ -981,22 +981,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ACA9C24-578D-43A9-82B8-6427B2AE2C72}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="4" width="52.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="25.3984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.3984375" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="4" width="52.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.3984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.3984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.3984375" style="1" customWidth="1"/>
     <col min="8" max="8" width="43" style="1" customWidth="1"/>
-    <col min="9" max="9" width="59.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="73.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="59.59765625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="73.73046875" style="1" customWidth="1"/>
     <col min="11" max="11" width="19" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.85546875" style="1"/>
+    <col min="12" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1004,13 +1004,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
@@ -1019,19 +1019,19 @@
         <v>17</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1039,34 +1039,34 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1074,34 +1074,34 @@
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="23" t="s">
         <v>7</v>
       </c>
@@ -1109,19 +1109,19 @@
         <v>8</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>10</v>
@@ -1130,13 +1130,13 @@
         <v>10</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="122.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="23" t="s">
         <v>11</v>
       </c>
@@ -1144,19 +1144,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>10</v>
@@ -1165,13 +1165,13 @@
         <v>10</v>
       </c>
       <c r="J5" s="25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="68.849999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="68.849999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="23" t="s">
         <v>3</v>
       </c>
@@ -1179,34 +1179,34 @@
         <v>8</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A7" s="23" t="s">
         <v>12</v>
       </c>
@@ -1214,34 +1214,34 @@
         <v>8</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H7" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="46.5" x14ac:dyDescent="0.45">
       <c r="A8" s="23" t="s">
         <v>6</v>
       </c>
@@ -1249,34 +1249,34 @@
         <v>8</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H8" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -1284,34 +1284,34 @@
         <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
@@ -1319,34 +1319,34 @@
         <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>3</v>
       </c>
@@ -1354,34 +1354,34 @@
         <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A12" s="13" t="s">
         <v>7</v>
       </c>
@@ -1389,34 +1389,34 @@
         <v>13</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A13" s="15" t="s">
         <v>6</v>
       </c>
@@ -1424,10 +1424,10 @@
         <v>13</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E13" s="15">
         <v>314</v>
@@ -1436,22 +1436,22 @@
         <v>5</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A14" s="15" t="s">
         <v>3</v>
       </c>
@@ -1459,10 +1459,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E14" s="31">
         <v>314334</v>
@@ -1471,22 +1471,22 @@
         <v>5</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
@@ -1494,34 +1494,34 @@
         <v>13</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J15" s="29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="s">
         <v>6</v>
       </c>
@@ -1529,34 +1529,34 @@
         <v>13</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="s">
         <v>3</v>
       </c>
@@ -1564,34 +1564,34 @@
         <v>13</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J17" s="29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A18" s="26" t="s">
         <v>12</v>
       </c>
@@ -1599,34 +1599,34 @@
         <v>13</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F18" s="26" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="I18" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="J18" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" s="27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A19" s="9" t="s">
         <v>3</v>
       </c>
@@ -1634,34 +1634,34 @@
         <v>15</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D19" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="J19" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K19" s="21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A20" s="9" t="s">
         <v>11</v>
       </c>
@@ -1669,34 +1669,34 @@
         <v>15</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D20" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="J20" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A21" s="9" t="s">
         <v>16</v>
       </c>
@@ -1704,34 +1704,34 @@
         <v>15</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D21" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="J21" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A22" s="11" t="s">
         <v>12</v>
       </c>
@@ -1739,42 +1739,42 @@
         <v>15</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K22" s="22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
     </row>
@@ -1797,15 +1797,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100EEE3694774EF754A8CC6FC6FA5E27970" ma:contentTypeVersion="13" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="d93f88a0a8255bfb930f7a727db686ad">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1f0a4303-6c30-4be1-95b2-d3f846a6dc61" xmlns:ns4="35f94e42-e4d5-4a2a-b205-129e91914919" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd2b915ebf31ecc04d3ae81b403b739a" ns3:_="" ns4:_="">
     <xsd:import namespace="1f0a4303-6c30-4be1-95b2-d3f846a6dc61"/>
@@ -2028,6 +2019,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9B5ECA8-FED0-4F9E-AF48-225E059A944A}">
   <ds:schemaRefs>
@@ -2046,14 +2046,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75168B6-E7FC-4BE5-9F9D-42A41711F424}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF3CE86-C263-48A8-AB0F-CFFD6601505F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2070,4 +2062,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75168B6-E7FC-4BE5-9F9D-42A41711F424}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>